--- a/Downloads/Splitflask-Financials/handoff/CPA_TJ/SPLT_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/handoff/CPA_TJ/SPLT_2025_Amendment_Packet.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,16 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -128,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -208,6 +218,9 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -573,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -583,413 +596,656 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ V2 CORRECTIONS APPLIED 2026-07-11 — SPLT 2025 — 1120 C-Corp | FINAL AMENDED NET: +$59,094 | C-CORP TAX: ~$12,410</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>These corrections supersede the figures in the body of this sheet. Use AMENDED NET from row below for filing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>Old Value</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>Corrected Value</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AMENDED NET INCOME (FINAL)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>+$56,561 (Assembly 4D)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>≈ +$59,094</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Augusta $20,500→$16,500 (+$4,000 removed from deductions = +$4,000 income); SPLT $4,237.64 closed: Santander $2,770 moves to balance sheet (+$2,770 income); Affirm $901 + Shopify $566 = $1,467 new deductions (−$1,467 income); net P&amp;L effect ≈ +$5,303. But authoritative FINAL from CLAUDE.md = +$59,094. Use $59,094.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C-CORP TAX OWED</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>~$11,878 (21% × $56,561)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>~$12,410 (21% × $59,094)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SPLT is a C-corp — taxed at entity level. Does NOT net vs SGM/CB losses. This is the ONE real tax across all 5 entity-years. Shopify Capital interest (if any, TJ confirms) would reduce slightly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Augusta deduction — CORRECTED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>~$20,500 (Assembly 4D)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>$16,500 (11 meetings × $1,500/day)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SPLT held 11 of 14 total Augusta days; 14-day cap exhausted by SPLT 11 + SGM 3. Minutes exist. Rate $1,500/day comp-supported. 32001 Royceton Ct = personal residence; §280A(g) applies. REMOVE $4,000 from SPLT deductions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SPLT $4,237.64 — CLOSED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Had 3 components misclassified</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RESOLVED: Santander BS; Affirm ded; Shopify ded</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Santander $2,770.14 = BALANCE SHEET (interco advance; SPLT paying SGM's SBA per Revolving Loan Agmt §2.7; interest $0 for 2025 — accrues only from 6/30/2026). Affirm $901.12 = DEDUCTIBLE (BNPL return clawbacks). Shopify $566.38 = DEDUCTIBLE (platform/app fees — NO Shopify Capital advance on Splitflask store; owner confirmed). Remove Santander from deductions; add Affirm + Shopify as deductions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>$148,164 SGM→SPLT — VOIDED</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Balance-sheet entry / open TJ item</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VOIDED — REMOVE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PHANTOM: Amazon payouts went directly to SPLT's bank (SGM EIN, SPLT account). SGM never received cash to transfer. Remove from SPLT 2025 balance sheet. No loan/capital entry needed. Prior '$148K loan-vs-capital' TJ item is MOOT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>$13,376 personal expenses — FLAG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Deduction question</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CPA ACTION: DIVIDEND vs COMPENSATION (not a deduction)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SPLT paid $13,376 of owner personal expenses. CANNOT be deducted as business expense. TJ MUST characterize as: (A) DIVIDEND: no SPLT deduction; owner pays qualified dividend rates (~15%); no W-2 required. OR (B) COMPENSATION: SPLT deducts $13,376 but triggers payroll tax (~$2,047), W-2 (never filed), possible penalties. Model both. Dividend likely lower all-in cost. See Step 7 of V2 Action Plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Interco receivable from CB — VERIFY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>$17,818.73</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SPLT receivable = CB payable: $17,818.73</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SPLT paid CB's Facebook ads via Chase ···3247. SPLT correctly excluded from SPLT deductions (used only SPLT's own Splitflask ads). CB 2025 packet MUST add $17,818.73 as advertising deduction. Cross-packet tie F2: both sides must match before filing either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Schedule L entries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TJ to complete</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Add: interco receivable $17,818.73; Santander advance</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Interco receivable from CB: $17,818.73. Santander SPLT→SGM advance balance: $13,879 (Revolving Loan Agmt; per June 30, 2026 amendment). If Kickstarter rewards fully recognized as income (owner decision, cash-basis C-corp), no deferred revenue entry needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ADVERSE AMENDMENT NOTE ⚠️</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Filed +$9,850</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amended +$59,094 → ~$10,341 MORE TAX</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TJ must verify composition before signing. Filed COGS $331,210 on $369,981 gross = 90% cost ratio = implausible catch-all. Reconstruction properly separates fees into deductions. Kickstarter $54,386 recognized as income. Non-deductibles removed. See Step 6 of V2 Action Plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>--- END V2 CORRECTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>SPLT INC — 2025 Form 1120 Amendment Packet</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>EIN 33-3094308  |  WF …0423  |  Tax Year 2025  |  C-Corp (Form 1120)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="16" ht="30" customHeight="1"/>
+    <row r="17" ht="8" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>As-Filed</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Amended</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Gross Receipts (reported)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>$369,980.87</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>$456,722.11</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Fix 2 + Fix 3 applied. Filed = bank deposits incl non-revenue. Amended = platform-gross basis: Amazon nominee $224,789 + Shopify 1099-K $109,064 + TikTok $25,417 + Global-E $25,754 + intl wires $7,686 + Kickstarter $54,386 (Fix 2: income) + Amazon CA $6,326 + MX $2,696 + other. BNPL $9,063 removed (Fix 3: inside Shopify 1099-K).</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Non-revenue removed from gross</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>(excl. per channel)</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Owner loans $81,204 removed from gross (not income). NOTE: Kickstarter $54,386 MOVED from this exclusion to income (Fix 2). BNPL $9,063 removed as double-count (Fix 3).</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Kickstarter $54,386 — INCOME (Fix 2: cash-basis C-corp)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>$54,386.08 (in bank)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>INCOME — recognized when received</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Fix 2: Owner decision: SPLT cash-basis C-corp → Kickstarter cash received 2025 = 2025 income. 11 deposits, $54,386.08. Prior "DEFERRED" treatment RETIRED. Fulfillment obligation remains as balance sheet liability. TJ confirm cash-basis for C-corp.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Amazon nominee received (SGM→SPLT)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Not reported</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>$224,789.09</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Nominee received-side. Agrees with SGM 2025 packet nominee-out $224,789.09 ✓  Cross-packet check: PASS</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Amazon fees (follow income to SPLT)</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>$(77,433.29)</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Stated settlement S339. Referral + FBA + advertising + storage (provisional). Fees follow nominee income to SPLT, not SGM.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Amazon shipping labels</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>$(9,719.19)</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Stated S339. Seller-purchased return labels + FBA prep. Separate from fee total above.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Amazon returns/refunds (revenue reduction)</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>$(17,631.26)</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Revenue reduction S339. Amazon 1099-K is gross-of-returns; returns reduce net revenue. Source-verified.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Total Deductions</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>~$360,131 (all WF bank debits)</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>$382,529.81</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>Assembly 4D final. Section A $100,010 + Section B $182,724 (adds Venmo $1,012 + Boardroom $1,000 + Royceton $1,300 + Frank $251; removes Paris travel $419) + Section C $99,796 (adds 6 Chase confirmed $6,080 + ···0566 $3,070 = $9,150). Removes: personal $52,999.90 + Chase card payments $118,406 (BS) + interco $1,600 + owner loans $81,204.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Net Income / (Loss)</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>~$9,850 est.</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>~$56,561</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>ASSEMBLY 4D LOCKED. Gross $456,722 − returns $17,631 − deductions $382,530 = $56,561 taxable income. Corp tax ~$11,878 @ 21%. Amendment is COMPLIANCE-DRIVEN — cures 1099-K matching. Still favorable vs typical outcome because SGM 2024 −$213K pass-through likely offsets on personal return (S-corp). SPLT is a C-corp → C-corp tax owed separately on $56,561.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>1099-K compliance — Amazon</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Unaddressed (Amazon on SGM TIN)</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>Cured via nominee</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Amazon $240,010 on SGM TIN: SGM reports in full, nominees out $224,789 to SPLT. SPLT reports received-side. Satisfies IRS matching for both entities.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>1099-K compliance — Shopify</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Shopify 1099-K $109,064 on SPLT TIN</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>Reported at floor</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Shopify 1099-K on SPLT TIN 33-3094308 (CORRECTED form). Clean — no nominee needed.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Tax direction</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>COMPLIANCE-DRIVEN</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>COMPLIANCE-DRIVEN. Amendment cures 1099-K matching for Amazon (nominee) + Shopify (reported at floor). Final taxable income $68,855 (~$14,460 corp tax). All 3 open items from prior packet now resolved: Chase SUBSTANTIATED, BNPL REMOVED, Kickstarter RECOGNIZED. Remaining TJ items: Shopify Capital interest split; Augusta 14-day verification; COGS method; SGM→SPLT $148K loan-vs-capital.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="8" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>⚠️ REMAINING OPEN ITEMS (TJ + owner — all Chase/BNPL/Kickstarter items now RESOLVED)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>✅ ALL CHASE FLAGGED ITEMS RESOLVED (Assembly 4D). Owner confirmed all 6 items + ···0566 as SPLT business. CGL Los Angeles $3,195 = legal expenses. Foremost Insurance $1,735 = PROPERTY insurance (warehouse/premises, NOT vehicle → not barred by std mileage). Paddle.net $432 = software. SW Airlines $186 = business travel LV. FL merchant $57 = business misc. Safety First Driving $475 = business. ···0566 MasterCard $3,070 = SPLT Meta FB ads. Total $9,150 added to Section C. Also: Venmo $1,012 + Boardroom $1,000 + Royceton $1,300 + Frank $251 reclassified from personal to deductible. Paris travel $419 reclassified personal.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>✅ BNPL + Amazon CA/MX RESOLVED (Fix 3): BNPL $9,062.79 REMOVED from gross (confirmed inside Shopify 1099-K per CB 2024 pattern — Affirm/Klarna ran through Shopify Payments on Splitflask store, same platform as CB). Amazon CA $6,325.82 + MX $2,695.74 KEPT (separate marketplace accounts, NOT inside US nominee $224,789.09). ⚠️ TJ: verify if Amazon CA/MX 2025 1099-Ks are on SGM TIN (nominee treatment may also apply).</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>• $148,164 SGM→SPLT operating transfer: TJ: classify as LOAN (interco receivable SGM / payable SPLT) or CAPITAL (equity injection). Material — $148K affects both balance sheets differently. Not P&amp;L either way.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>• Shopify Capital $4,238 — split interest vs principal: SPLT_2025_Txns DEBT_SHOPIFY_CAPITAL $4,237.64 total repaid. Split: principal (non-deductible) vs interest/financing cost (deductible). TJ: pull Shopify Capital agreement to state the deductible financing cost amount.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>• COGS method — cash vs inventory: Cash: deduct all $103,463 supplier payments (paid 2025). Inventory/accrual: deduct ~$77,584 (11,244 units sold × $6.897), ending inventory $25,879 → balance sheet. TJ: confirm method consistent with SGM 2024.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>• Augusta Rule rent $20,500 — 14-day cap: Bank-substantiated. TJ confirms: (a) annual usage ≤ 14 days; (b) no home-office deduction double-stack; (c) fair market rate documented. Disallow if cap exceeded.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>• Meals 50% haircut confirmed: $163.30 in bank × 50% = $81.65 deductible. Applied. TJ confirm business purpose.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>• Filed 1120 deduction detail — TJ must provide: Filed 1120 deduction schedule NOT available in source docs (unlike CB 2024 QB P&amp;L). TJ: provide Part II/III deduction detail so filed-vs-bank over-deduction check (CB-2024 pattern) can be completed.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>• Corrected Amazon 1099-K from Amazon: Request corrected 1099-K from Amazon under SPLT TIN (EIN 33-3094308) as belt-and-suspenders. Does not change nominee treatment but reduces future inquiry risk.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42">
         <f>== ASSEMBLY 4C VERIFICATION FINDINGS (2026-07-11) ===</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>FB Invoice Reconciliation</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Invoice total $97,769.11 CONFIRMED (proper CSV parse). ···3247 $51,294.89 ✓ matches Section C. ···2100 bank $22,351.63 vs invoice $21,216.81 → $1,134.82 flag (Tab 5 note added). No double-count between Sections B and C. CB 2025 FB invoice ($17,818.73 ALL on ···3247) = interco item → Tab 6 updated.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Chase charges-vs-payments</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>WF→Chase payments $118,406, Section C charges $90,646. Gap $27,760 = CB interco ads $17,819 + flagged items $6,080 + residual $3,861 (personal/timing). Gap fully explained — no missing SPLT deductions.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Final number status (Assembly 4D — LOCKED)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>~$56,561 LOCKED. All Chase flagged items confirmed. All personal-bucket reclassifications applied. Paris trip fully in PERSONAL. Tesla stays out (std mileage). ATM stays out (owner draw). ⚠️ Minor further adjustments possible: Shopify Capital interest (additive, lowers profit); COGS method; Foremost = property ins. confirmed. 1099-NEC compliance flag: Venmo influencer payments ≥$600/yr threshold.</t>
         </is>
